--- a/Ranjeet python excelsheet.xlsx
+++ b/Ranjeet python excelsheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9e3ae0a68ad54d6/Desktop/c^M^M mca/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9e3ae0a68ad54d6/Desktop/github/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{B70CB022-4598-4371-8C12-1AB2E557F6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B4770B9-FF59-4467-A03D-6188F2292438}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{B70CB022-4598-4371-8C12-1AB2E557F6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3253B8DF-EB47-4CD3-954A-D7A38FF0BBD3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1073,26 +1073,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B8" s="14">
+        <v>450</v>
+      </c>
+      <c r="C8" s="14">
+        <v>50</v>
+      </c>
+      <c r="D8" s="14">
+        <v>260</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>200</v>
+      </c>
+      <c r="G8" s="14">
+        <v>4</v>
+      </c>
+      <c r="H8" s="14">
+        <v>60</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/Ranjeet python excelsheet.xlsx
+++ b/Ranjeet python excelsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9e3ae0a68ad54d6/Desktop/github/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="14_{769DAEC6-8838-43B9-AE9A-1AFFE7820891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31A68D8A-23C9-4542-B776-941FF6DE8151}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="14_{769DAEC6-8838-43B9-AE9A-1AFFE7820891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{453A802B-8249-4778-8099-DDE6BD8AD35F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2629,21 +2629,21 @@
         <v>45</v>
       </c>
       <c r="F40" s="14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G40" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H40" s="14">
         <v>120</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="2"/>
-        <v>1130</v>
+        <v>1180</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="3"/>
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>55</v>
@@ -2659,26 +2659,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B41" s="14">
+        <v>420</v>
+      </c>
+      <c r="C41" s="14">
+        <v>60</v>
+      </c>
+      <c r="D41" s="14">
+        <v>240</v>
+      </c>
+      <c r="E41" s="14">
+        <v>60</v>
+      </c>
+      <c r="F41" s="14">
+        <v>200</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
+      <c r="H41" s="14">
+        <v>60</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
